--- a/mismatch/verse_mismatch.xlsx
+++ b/mismatch/verse_mismatch.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="21920" activeTab="1"/>
+    <workbookView windowHeight="21920"/>
   </bookViews>
   <sheets>
     <sheet name="不一致记录" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="244">
   <si>
     <t>txt文件名</t>
   </si>
@@ -42,6 +42,12 @@
     <t>1Chr_12_en.txt</t>
   </si>
   <si>
+    <t>nrsvce和思高印刷版一样，但和万有真原不一样</t>
+  </si>
+  <si>
+    <t>英的4-5相当于中的5</t>
+  </si>
+  <si>
     <t>1Chr_5_en.txt</t>
   </si>
   <si>
@@ -49,6 +55,9 @@
   </si>
   <si>
     <t>1K_22_en.txt</t>
+  </si>
+  <si>
+    <t>nrsvce和中文不一样</t>
   </si>
   <si>
     <t>1K_4_en.txt</t>
@@ -763,14 +772,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1226,148 +1228,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1719,10 +1721,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C235"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <dimension ref="A1:E235"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="64.1953125" customWidth="1"/>
+    <col min="4" max="4" width="39.84375" customWidth="1"/>
+    <col min="5" max="5" width="20.4453125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1733,7 +1740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1743,10 +1750,16 @@
       <c r="C2">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>26</v>
@@ -1754,10 +1767,13 @@
       <c r="C3">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>81</v>
@@ -1765,10 +1781,13 @@
       <c r="C4">
         <v>66</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>53</v>
@@ -1776,10 +1795,13 @@
       <c r="C5">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>34</v>
@@ -1787,10 +1809,13 @@
       <c r="C6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>18</v>
@@ -1798,10 +1823,13 @@
       <c r="C7">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>15</v>
@@ -1810,9 +1838,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>29</v>
@@ -1821,9 +1849,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>22</v>
@@ -1832,9 +1860,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>22</v>
@@ -1843,9 +1871,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>15</v>
@@ -1854,9 +1882,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>17</v>
@@ -1865,9 +1893,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>18</v>
@@ -1876,9 +1904,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>21</v>
@@ -1887,9 +1915,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>21</v>
@@ -1900,7 +1928,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>33</v>
@@ -1911,7 +1939,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>43</v>
@@ -1922,7 +1950,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>40</v>
@@ -1933,7 +1961,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>41</v>
@@ -1944,7 +1972,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>26</v>
@@ -1955,7 +1983,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>30</v>
@@ -1966,7 +1994,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>39</v>
@@ -1977,7 +2005,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>37</v>
@@ -1988,7 +2016,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B25">
         <v>73</v>
@@ -1999,7 +2027,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B26">
         <v>42</v>
@@ -2010,7 +2038,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>97</v>
@@ -2021,7 +2049,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B28">
         <v>37</v>
@@ -2032,7 +2060,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>31</v>
@@ -2043,7 +2071,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>28</v>
@@ -2054,7 +2082,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B31">
         <v>32</v>
@@ -2065,7 +2093,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B32">
         <v>18</v>
@@ -2076,7 +2104,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B33">
         <v>30</v>
@@ -2087,7 +2115,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B34">
         <v>25</v>
@@ -2098,7 +2126,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B35">
         <v>68</v>
@@ -2109,7 +2137,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B36">
         <v>29</v>
@@ -2120,7 +2148,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B37">
         <v>16</v>
@@ -2131,7 +2159,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B38">
         <v>20</v>
@@ -2142,7 +2170,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2153,7 +2181,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2164,7 +2192,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2175,7 +2203,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2186,7 +2214,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2197,7 +2225,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2208,7 +2236,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B45">
         <v>37</v>
@@ -2219,7 +2247,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B46">
         <v>23</v>
@@ -2230,7 +2258,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B47">
         <v>21</v>
@@ -2241,7 +2269,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B48">
         <v>17</v>
@@ -2252,7 +2280,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B49">
         <v>56</v>
@@ -2263,7 +2291,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B50">
         <v>14</v>
@@ -2274,7 +2302,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B51">
         <v>10</v>
@@ -2285,7 +2313,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B52">
         <v>40</v>
@@ -2296,7 +2324,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B53">
         <v>32</v>
@@ -2307,7 +2335,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B54">
         <v>36</v>
@@ -2318,7 +2346,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B55">
         <v>31</v>
@@ -2329,7 +2357,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B56">
         <v>25</v>
@@ -2340,7 +2368,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B57">
         <v>32</v>
@@ -2351,7 +2379,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B58">
         <v>49</v>
@@ -2362,7 +2390,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B59">
         <v>32</v>
@@ -2373,7 +2401,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B60">
         <v>55</v>
@@ -2384,7 +2412,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B61">
         <v>32</v>
@@ -2395,7 +2423,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B62">
         <v>24</v>
@@ -2406,7 +2434,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B63">
         <v>12</v>
@@ -2417,7 +2445,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B64">
         <v>14</v>
@@ -2428,7 +2456,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B65">
         <v>16</v>
@@ -2439,7 +2467,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B66">
         <v>9</v>
@@ -2450,7 +2478,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B67">
         <v>11</v>
@@ -2461,7 +2489,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B68">
         <v>23</v>
@@ -2472,7 +2500,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B69">
         <v>24</v>
@@ -2483,7 +2511,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B70">
         <v>12</v>
@@ -2494,7 +2522,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B71">
         <v>25</v>
@@ -2505,7 +2533,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B72">
         <v>22</v>
@@ -2516,7 +2544,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B73">
         <v>21</v>
@@ -2527,7 +2555,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B74">
         <v>26</v>
@@ -2538,7 +2566,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B75">
         <v>22</v>
@@ -2549,7 +2577,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B76">
         <v>26</v>
@@ -2560,7 +2588,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B77">
         <v>32</v>
@@ -2571,7 +2599,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B78">
         <v>21</v>
@@ -2582,7 +2610,7 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2593,7 +2621,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B80">
         <v>46</v>
@@ -2604,7 +2632,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B81">
         <v>25</v>
@@ -2615,7 +2643,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B82">
         <v>23</v>
@@ -2626,7 +2654,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B83">
         <v>24</v>
@@ -2637,7 +2665,7 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B84">
         <v>34</v>
@@ -2648,7 +2676,7 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B85">
         <v>17</v>
@@ -2659,7 +2687,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B86">
         <v>10</v>
@@ -2670,7 +2698,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B87">
         <v>19</v>
@@ -2681,7 +2709,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B88">
         <v>30</v>
@@ -2692,7 +2720,7 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B89">
         <v>36</v>
@@ -2703,7 +2731,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B90">
         <v>55</v>
@@ -2714,7 +2742,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B91">
         <v>18</v>
@@ -2725,7 +2753,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B92">
         <v>13</v>
@@ -2736,7 +2764,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B93">
         <v>15</v>
@@ -2747,7 +2775,7 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B94">
         <v>32</v>
@@ -2758,7 +2786,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B95">
         <v>46</v>
@@ -2769,7 +2797,7 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B96">
         <v>36</v>
@@ -2780,7 +2808,7 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B97">
         <v>48</v>
@@ -2791,7 +2819,7 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B98">
         <v>26</v>
@@ -2802,7 +2830,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B99">
         <v>34</v>
@@ -2813,7 +2841,7 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B100">
         <v>38</v>
@@ -2824,7 +2852,7 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B101">
         <v>39</v>
@@ -2835,7 +2863,7 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B102">
         <v>32</v>
@@ -2846,7 +2874,7 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B103">
         <v>23</v>
@@ -2857,7 +2885,7 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B104">
         <v>73</v>
@@ -2868,7 +2896,7 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B105">
         <v>38</v>
@@ -2879,7 +2907,7 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B106">
         <v>15</v>
@@ -2890,7 +2918,7 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B107">
         <v>13</v>
@@ -2901,7 +2929,7 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B108">
         <v>50</v>
@@ -2912,7 +2940,7 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B109">
         <v>13</v>
@@ -2923,7 +2951,7 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B110">
         <v>40</v>
@@ -2934,7 +2962,7 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B111">
         <v>16</v>
@@ -2945,7 +2973,7 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B112">
         <v>6</v>
@@ -2956,7 +2984,7 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B113">
         <v>9</v>
@@ -2967,7 +2995,7 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B114">
         <v>23</v>
@@ -2978,7 +3006,7 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B115">
         <v>32</v>
@@ -2989,7 +3017,7 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B116">
         <v>8</v>
@@ -3000,7 +3028,7 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B117">
         <v>8</v>
@@ -3011,7 +3039,7 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B118">
         <v>8</v>
@@ -3022,7 +3050,7 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B119">
         <v>9</v>
@@ -3033,7 +3061,7 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B120">
         <v>10</v>
@@ -3044,7 +3072,7 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B121">
         <v>5</v>
@@ -3055,7 +3083,7 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B122">
         <v>9</v>
@@ -3066,7 +3094,7 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B123">
         <v>6</v>
@@ -3077,7 +3105,7 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B124">
         <v>7</v>
@@ -3088,7 +3116,7 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B125">
         <v>6</v>
@@ -3099,7 +3127,7 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B126">
         <v>7</v>
@@ -3110,7 +3138,7 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B127">
         <v>9</v>
@@ -3121,7 +3149,7 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B128">
         <v>9</v>
@@ -3132,7 +3160,7 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B129">
         <v>4</v>
@@ -3143,7 +3171,7 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B130">
         <v>19</v>
@@ -3154,7 +3182,7 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B131">
         <v>4</v>
@@ -3165,7 +3193,7 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B132">
         <v>4</v>
@@ -3176,7 +3204,7 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B133">
         <v>9</v>
@@ -3187,7 +3215,7 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B134">
         <v>25</v>
@@ -3198,7 +3226,7 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B135">
         <v>7</v>
@@ -3209,7 +3237,7 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B136">
         <v>11</v>
@@ -3220,7 +3248,7 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B137">
         <v>13</v>
@@ -3231,7 +3259,7 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B138">
         <v>16</v>
@@ -3242,7 +3270,7 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B139">
         <v>22</v>
@@ -3253,7 +3281,7 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B140">
         <v>8</v>
@@ -3264,7 +3292,7 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B141">
         <v>6</v>
@@ -3275,7 +3303,7 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B142">
         <v>12</v>
@@ -3286,7 +3314,7 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B143">
         <v>16</v>
@@ -3297,7 +3325,7 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B144">
         <v>7</v>
@@ -3308,7 +3336,7 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B145">
         <v>11</v>
@@ -3319,7 +3347,7 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B146">
         <v>23</v>
@@ -3330,7 +3358,7 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B147">
         <v>13</v>
@@ -3341,7 +3369,7 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B148">
         <v>15</v>
@@ -3352,7 +3380,7 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B149">
         <v>10</v>
@@ -3363,7 +3391,7 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B150">
         <v>12</v>
@@ -3374,7 +3402,7 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B151">
         <v>12</v>
@@ -3385,7 +3413,7 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B152">
         <v>29</v>
@@ -3396,7 +3424,7 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B153">
         <v>41</v>
@@ -3407,7 +3435,7 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B154">
         <v>24</v>
@@ -3418,7 +3446,7 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B155">
         <v>20</v>
@@ -3429,7 +3457,7 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B156">
         <v>10</v>
@@ -3440,7 +3468,7 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B157">
         <v>8</v>
@@ -3451,7 +3479,7 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B158">
         <v>13</v>
@@ -3462,7 +3490,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B159">
         <v>21</v>
@@ -3473,7 +3501,7 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B160">
         <v>21</v>
@@ -3484,7 +3512,7 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B161">
         <v>29</v>
@@ -3495,7 +3523,7 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B162">
         <v>24</v>
@@ -3506,7 +3534,7 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B163">
         <v>73</v>
@@ -3517,7 +3545,7 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B164">
         <v>14</v>
@@ -3528,7 +3556,7 @@
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B165">
         <v>9</v>
@@ -3539,7 +3567,7 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B166">
         <v>18</v>
@@ -3550,7 +3578,7 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B167">
         <v>8</v>
@@ -3561,7 +3589,7 @@
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B168">
         <v>18</v>
@@ -3572,7 +3600,7 @@
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B169">
         <v>10</v>
@@ -3583,7 +3611,7 @@
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B170">
         <v>26</v>
@@ -3594,7 +3622,7 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B171">
         <v>30</v>
@@ -3605,7 +3633,7 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B172">
         <v>32</v>
@@ -3616,7 +3644,7 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B173">
         <v>18</v>
@@ -3627,7 +3655,7 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B174">
         <v>25</v>
@@ -3638,7 +3666,7 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B175">
         <v>20</v>
@@ -3649,7 +3677,7 @@
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B176">
         <v>28</v>
@@ -3660,7 +3688,7 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B177">
         <v>28</v>
@@ -3671,7 +3699,7 @@
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B178">
         <v>32</v>
@@ -3682,7 +3710,7 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B179">
         <v>27</v>
@@ -3693,7 +3721,7 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B180">
         <v>27</v>
@@ -3704,7 +3732,7 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B181">
         <v>31</v>
@@ -3715,7 +3743,7 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B182">
         <v>28</v>
@@ -3726,7 +3754,7 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B183">
         <v>25</v>
@@ -3737,7 +3765,7 @@
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B184">
         <v>27</v>
@@ -3748,7 +3776,7 @@
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B185">
         <v>32</v>
@@ -3759,7 +3787,7 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B186">
         <v>25</v>
@@ -3770,7 +3798,7 @@
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B187">
         <v>29</v>
@@ -3781,7 +3809,7 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B188">
         <v>30</v>
@@ -3792,7 +3820,7 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B189">
         <v>28</v>
@@ -3803,7 +3831,7 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B190">
         <v>28</v>
@@ -3814,7 +3842,7 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B191">
         <v>18</v>
@@ -3825,7 +3853,7 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B192">
         <v>25</v>
@@ -3836,7 +3864,7 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B193">
         <v>31</v>
@@ -3847,7 +3875,7 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B194">
         <v>24</v>
@@ -3858,7 +3886,7 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B195">
         <v>29</v>
@@ -3869,7 +3897,7 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B196">
         <v>31</v>
@@ -3880,7 +3908,7 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B197">
         <v>34</v>
@@ -3891,7 +3919,7 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B198">
         <v>35</v>
@@ -3902,7 +3930,7 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B199">
         <v>30</v>
@@ -3913,7 +3941,7 @@
     </row>
     <row r="200" spans="1:3">
       <c r="A200" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B200">
         <v>30</v>
@@ -3924,7 +3952,7 @@
     </row>
     <row r="201" spans="1:3">
       <c r="A201" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B201">
         <v>22</v>
@@ -3935,7 +3963,7 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B202">
         <v>25</v>
@@ -3946,7 +3974,7 @@
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B203">
         <v>34</v>
@@ -3957,7 +3985,7 @@
     </row>
     <row r="204" spans="1:3">
       <c r="A204" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B204">
         <v>23</v>
@@ -3968,7 +3996,7 @@
     </row>
     <row r="205" spans="1:3">
       <c r="A205" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B205">
         <v>26</v>
@@ -3979,7 +4007,7 @@
     </row>
     <row r="206" spans="1:3">
       <c r="A206" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B206">
         <v>20</v>
@@ -3990,7 +4018,7 @@
     </row>
     <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B207">
         <v>25</v>
@@ -4001,7 +4029,7 @@
     </row>
     <row r="208" spans="1:3">
       <c r="A208" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B208">
         <v>25</v>
@@ -4012,7 +4040,7 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B209">
         <v>16</v>
@@ -4023,7 +4051,7 @@
     </row>
     <row r="210" spans="1:3">
       <c r="A210" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B210">
         <v>31</v>
@@ -4034,7 +4062,7 @@
     </row>
     <row r="211" spans="1:3">
       <c r="A211" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B211">
         <v>29</v>
@@ -4045,7 +4073,7 @@
     </row>
     <row r="212" spans="1:3">
       <c r="A212" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B212">
         <v>30</v>
@@ -4056,7 +4084,7 @@
     </row>
     <row r="213" spans="1:3">
       <c r="A213" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B213">
         <v>15</v>
@@ -4067,7 +4095,7 @@
     </row>
     <row r="214" spans="1:3">
       <c r="A214" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B214">
         <v>36</v>
@@ -4078,7 +4106,7 @@
     </row>
     <row r="215" spans="1:3">
       <c r="A215" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B215">
         <v>19</v>
@@ -4089,7 +4117,7 @@
     </row>
     <row r="216" spans="1:3">
       <c r="A216" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B216">
         <v>18</v>
@@ -4100,7 +4128,7 @@
     </row>
     <row r="217" spans="1:3">
       <c r="A217" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B217">
         <v>13</v>
@@ -4111,7 +4139,7 @@
     </row>
     <row r="218" spans="1:3">
       <c r="A218" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B218">
         <v>13</v>
@@ -4122,7 +4150,7 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B219">
         <v>14</v>
@@ -4133,7 +4161,7 @@
     </row>
     <row r="220" spans="1:3">
       <c r="A220" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B220">
         <v>13</v>
@@ -4144,7 +4172,7 @@
     </row>
     <row r="221" spans="1:3">
       <c r="A221" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B221">
         <v>18</v>
@@ -4155,7 +4183,7 @@
     </row>
     <row r="222" spans="1:3">
       <c r="A222" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B222">
         <v>17</v>
@@ -4166,7 +4194,7 @@
     </row>
     <row r="223" spans="1:3">
       <c r="A223" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B223">
         <v>14</v>
@@ -4177,7 +4205,7 @@
     </row>
     <row r="224" spans="1:3">
       <c r="A224" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B224">
         <v>22</v>
@@ -4188,7 +4216,7 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B225">
         <v>18</v>
@@ -4199,7 +4227,7 @@
     </row>
     <row r="226" spans="1:3">
       <c r="A226" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B226">
         <v>16</v>
@@ -4210,7 +4238,7 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B227">
         <v>26</v>
@@ -4221,7 +4249,7 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B228">
         <v>21</v>
@@ -4232,7 +4260,7 @@
     </row>
     <row r="229" spans="1:3">
       <c r="A229" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B229">
         <v>24</v>
@@ -4243,7 +4271,7 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B230">
         <v>23</v>
@@ -4254,7 +4282,7 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B231">
         <v>25</v>
@@ -4265,7 +4293,7 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B232">
         <v>18</v>
@@ -4276,7 +4304,7 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B233">
         <v>21</v>
@@ -4287,7 +4315,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B234">
         <v>13</v>
@@ -4298,7 +4326,7 @@
     </row>
     <row r="235" spans="1:3">
       <c r="A235" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B235">
         <v>14</v>
@@ -4324,19 +4352,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C2"/>
+        <v>242</v>
+      </c>
       <c r="F2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
